--- a/12605178.xlsx
+++ b/12605178.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>Notes making and some personal work also.And pratice to build topology also using CISCO packet tracer</t>
+  </si>
+  <si>
+    <t>Stressed, and very different feeling coming out means very low.</t>
   </si>
 </sst>
 </file>
@@ -1647,27 +1650,51 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+    <row r="19" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="13">
+        <v>46227</v>
+      </c>
+      <c r="B19" s="14">
+        <v>450</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>0</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="14">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
